--- a/product_selector_out/STM8AL series.xlsx
+++ b/product_selector_out/STM8AL series.xlsx
@@ -2887,7 +2887,7 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6775,19 +6775,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z23" s="6" t="inlineStr">
@@ -6825,9 +6825,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6952,9 +6952,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z24" s="6" t="inlineStr">
@@ -6992,9 +6992,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7109,19 +7109,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z25" s="6" t="inlineStr">
@@ -7159,9 +7159,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7286,9 +7286,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z26" s="6" t="inlineStr">
@@ -7326,9 +7326,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7443,19 +7443,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z27" s="6" t="inlineStr">
@@ -7493,9 +7493,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7620,9 +7620,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y28" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z28" s="6" t="inlineStr">
@@ -7660,9 +7660,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7787,9 +7787,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y29" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z29" s="6" t="inlineStr">
@@ -7827,9 +7827,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7954,9 +7954,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y30" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z30" s="6" t="inlineStr">
@@ -7994,9 +7994,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8111,19 +8111,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X31" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y31" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z31" s="6" t="inlineStr">
@@ -8161,9 +8161,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8288,9 +8288,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y32" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z32" s="6" t="inlineStr">
@@ -8328,9 +8328,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8837,314 +8837,6 @@
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM8AL3L68</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM8AL3L68</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM8AL3L8A</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM8AL3L48</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM8AL3L48</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM8AL3L89</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM8AL3L46</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM8AL3L46</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM8AL3LE8A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM8AL3LE88</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM8AL3LE89</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM8AL3L66</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM8AL3L66</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM8AL3L88</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
         <is>
           <t>Table 29. Current consumption under external reset</t>
         </is>

--- a/product_selector_out/STM8AL series.xlsx
+++ b/product_selector_out/STM8AL series.xlsx
@@ -2887,7 +2887,7 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
     </row>
@@ -6775,19 +6775,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="X23" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z23" s="6" t="inlineStr">
@@ -6825,9 +6825,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6952,9 +6952,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z24" s="6" t="inlineStr">
@@ -6992,9 +6992,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7109,19 +7109,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="X25" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z25" s="6" t="inlineStr">
@@ -7159,9 +7159,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7286,9 +7286,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z26" s="6" t="inlineStr">
@@ -7326,9 +7326,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7443,19 +7443,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="X27" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z27" s="6" t="inlineStr">
@@ -7493,9 +7493,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7620,9 +7620,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y28" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z28" s="6" t="inlineStr">
@@ -7660,9 +7660,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7787,9 +7787,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y29" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z29" s="6" t="inlineStr">
@@ -7827,9 +7827,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7954,9 +7954,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y30" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z30" s="6" t="inlineStr">
@@ -7994,9 +7994,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG30" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8111,19 +8111,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="X31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="Y31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="X31" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="Y31" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z31" s="6" t="inlineStr">
@@ -8161,9 +8161,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG31" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8288,9 +8288,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="Y32" s="8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="Z32" s="6" t="inlineStr">
@@ -8328,9 +8328,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG32" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AG32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8842,6 +8842,314 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM8AL3L68</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM8AL3L68</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM8AL3L8A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM8AL3L48</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM8AL3L48</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM8AL3L89</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM8AL3L46</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM8AL3L46</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM8AL3LE8A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM8AL3LE88</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM8AL3LE89</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM8AL3L66</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM8AL3L66</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM8AL3L88</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 29. Current consumption under external reset</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM8AL series.xlsx
+++ b/product_selector_out/STM8AL series.xlsx
@@ -2887,7 +2887,7 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6775,19 +6775,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z23" s="6" t="inlineStr">
@@ -6825,9 +6825,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6952,9 +6952,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z24" s="6" t="inlineStr">
@@ -6992,9 +6992,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7109,19 +7109,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z25" s="6" t="inlineStr">
@@ -7159,9 +7159,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7286,9 +7286,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z26" s="6" t="inlineStr">
@@ -7326,9 +7326,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7443,19 +7443,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X27" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z27" s="6" t="inlineStr">
@@ -7493,9 +7493,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7620,9 +7620,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y28" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z28" s="6" t="inlineStr">
@@ -7660,9 +7660,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7787,9 +7787,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y29" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z29" s="6" t="inlineStr">
@@ -7827,9 +7827,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7954,9 +7954,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y30" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z30" s="6" t="inlineStr">
@@ -7994,9 +7994,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8111,19 +8111,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="X31" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="Y31" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="W31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="X31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="Y31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z31" s="6" t="inlineStr">
@@ -8161,9 +8161,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8288,9 +8288,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y32" s="8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="Y32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="Z32" s="6" t="inlineStr">
@@ -8328,9 +8328,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AG32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8842,314 +8842,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM8AL3L68</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM8AL3L68</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM8AL3L8A</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM8AL3L48</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM8AL3L48</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM8AL3L89</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM8AL3L46</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM8AL3L46</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM8AL3LE8A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM8AL3LE88</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM8AL3LE89</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM8AL3L66</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.65(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM8AL3L66</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM8AL3L88</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 29. Current consumption under external reset</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM8AL series.xlsx
+++ b/product_selector_out/STM8AL series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG32"/>
+  <dimension ref="A1:AH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,8 @@
     <col width="23.46484375" customWidth="1" min="30" max="30"/>
     <col width="11.6328125" customWidth="1" min="31" max="31"/>
     <col width="43.6484375" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -716,6 +717,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -883,6 +889,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -1050,6 +1061,11 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -1217,6 +1233,11 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -1384,6 +1405,11 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -1551,6 +1577,11 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -1718,6 +1749,11 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -1885,6 +1921,11 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -2052,6 +2093,11 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -2219,6 +2265,11 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3136.pdf</t>
         </is>
       </c>
@@ -2386,6 +2437,11 @@
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al31e88.pdf</t>
         </is>
       </c>
@@ -2553,6 +2609,11 @@
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
@@ -2720,6 +2781,11 @@
       </c>
       <c r="AG22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8al3188.pdf</t>
         </is>
       </c>
@@ -2890,6 +2956,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -3057,6 +3128,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -3224,6 +3300,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3391,6 +3472,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -3558,6 +3644,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3725,6 +3816,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3892,6 +3988,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -4059,6 +4160,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -4226,6 +4332,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -4393,11 +4504,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -4434,7 +4550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG32"/>
+  <dimension ref="A1:AH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4470,6 +4586,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4656,6 +4773,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -4821,7 +4943,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4988,7 +5115,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5155,7 +5287,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG13" s="6" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5322,7 +5459,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG14" s="6" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5489,7 +5631,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG15" s="6" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5656,7 +5803,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG16" s="6" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5823,7 +5975,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG17" s="6" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5990,7 +6147,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG18" s="6" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6157,7 +6319,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG19" s="6" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6324,7 +6491,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG20" s="6" t="inlineStr">
+      <c r="AG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6491,7 +6663,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG21" s="6" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6658,7 +6835,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG22" s="6" t="inlineStr">
+      <c r="AG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6830,6 +7012,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -6997,6 +7184,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -7164,6 +7356,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -7331,6 +7528,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -7498,6 +7700,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -7665,6 +7872,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -7832,6 +8044,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -7999,6 +8216,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -8166,6 +8388,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -8333,11 +8560,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="AH32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
